--- a/real_estate_forms/021_real_estate_data_integration_application_form--real_estate_forms.xlsx
+++ b/real_estate_forms/021_real_estate_data_integration_application_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>property_type</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Property Type</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>real_estate_data_integration_form_property_details_choices</t>
+          <t>property_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>property_type</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Property Type</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1182,29 +1182,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>property_status_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>single_family_home</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Single Family Home</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>single_family_home</t>
+          <t>multi_family_home</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Single Family Home</t>
+          <t>Multi Family Home</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>multi_family_home</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Multi Family Home</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>condo</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>townhouse</t>
+          <t>duplex</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Duplex</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>listing_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>duplex</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Duplex</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1301,27 +1301,10 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>listing_type_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
